--- a/table/Supplementary Table 7.xlsx
+++ b/table/Supplementary Table 7.xlsx
@@ -1750,16 +1750,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>13513.84832241552</v>
+        <v>13513.85</v>
       </c>
       <c r="C2">
-        <v>13652.93797022442</v>
+        <v>13652.94</v>
       </c>
       <c r="D2">
-        <v>1.029237893533241</v>
+        <v>1.03</v>
       </c>
       <c r="E2">
-        <v>0.03103443000165296</v>
+        <v>0.031</v>
       </c>
       <c r="F2">
         <v>13513.84832241552</v>
@@ -1778,16 +1778,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>57351.02733142021</v>
+        <v>57351.03</v>
       </c>
       <c r="C3">
-        <v>60365.1625571617</v>
+        <v>60365.16</v>
       </c>
       <c r="D3">
-        <v>5.2555906423845</v>
+        <v>5.26</v>
       </c>
       <c r="E3">
-        <v>0.1553368954030798</v>
+        <v>0.155</v>
       </c>
       <c r="F3">
         <v>57351.02733142021</v>
@@ -1806,16 +1806,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>142924.1507636413</v>
+        <v>142924.15</v>
       </c>
       <c r="C4">
-        <v>140261.0422245954</v>
+        <v>140261.04</v>
       </c>
       <c r="D4">
-        <v>-1.863301985575561</v>
+        <v>-1.86</v>
       </c>
       <c r="E4">
-        <v>-0.05698012851151901</v>
+        <v>-0.057</v>
       </c>
       <c r="F4">
         <v>140184.6124583052</v>
@@ -1884,13 +1884,13 @@
         <v>406829.790100615</v>
       </c>
       <c r="C2">
-        <v>5.55442188868311</v>
+        <v>5.55</v>
       </c>
       <c r="D2">
         <v>1.00841318976099</v>
       </c>
       <c r="E2">
-        <v>5.60115229404523</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="3">
@@ -1903,13 +1903,13 @@
         <v>3495999.80502254</v>
       </c>
       <c r="C3">
-        <v>211.036596529991</v>
+        <v>211.04</v>
       </c>
       <c r="D3">
         <v>1.04279897543105</v>
       </c>
       <c r="E3">
-        <v>220.068746639932</v>
+        <v>220.07</v>
       </c>
     </row>
     <row r="4">
@@ -1922,13 +1922,13 @@
         <v>6976051.60944215</v>
       </c>
       <c r="C4">
-        <v>978.468269352922</v>
+        <v>978.47</v>
       </c>
       <c r="D4">
         <v>0.984728786423946</v>
       </c>
       <c r="E4">
-        <v>963.525871434242</v>
+        <v>963.53</v>
       </c>
     </row>
     <row r="5">
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="G5">
-        <v>1195.0592877716</v>
+        <v>1195.06</v>
       </c>
     </row>
     <row r="6">
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="G6">
-        <v>1189.19577036822</v>
+        <v>1189.2</v>
       </c>
     </row>
     <row r="7">
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="G7">
-        <v>-0.490646569871134</v>
+        <v>-0.49</v>
       </c>
     </row>
   </sheetData>
